--- a/hysteresis_summary.xlsx
+++ b/hysteresis_summary.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4BBFAB-61AE-49FE-A4BA-5C798CD0C683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A391F6-4573-4525-8A1F-57AE0952071D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SSC - Turbidity " sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="43">
   <si>
     <t>Storm</t>
   </si>
@@ -130,17 +131,57 @@
   <si>
     <t>* Extrapolated for Lawler</t>
   </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Event_1</t>
+  </si>
+  <si>
+    <t>Event_2</t>
+  </si>
+  <si>
+    <t>Event_3</t>
+  </si>
+  <si>
+    <t>Event_6</t>
+  </si>
+  <si>
+    <t>Event_7</t>
+  </si>
+  <si>
+    <t>Event_8</t>
+  </si>
+  <si>
+    <t>Event_9</t>
+  </si>
+  <si>
+    <t>Event_10</t>
+  </si>
+  <si>
+    <t>Event_12</t>
+  </si>
+  <si>
+    <t>Event_13</t>
+  </si>
+  <si>
+    <t>Event_14</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0000000"/>
-    <numFmt numFmtId="166" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,8 +189,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,6 +216,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -181,18 +247,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -204,13 +270,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -228,6 +320,2984 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Summer SSC HI to Turbidity HI  </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13638095238095238"/>
+          <c:y val="4.8096202503948055E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Langlois (2005)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.43146544181977253"/>
+                  <c:y val="-3.6791338582677122E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$C$4:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>5.5990042925280497</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6150481998819401</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1746388039620901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2792285281778502</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4480475262282899</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.45242884682964</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.84619083652769</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$H$4:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.7878260187067601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8770644107042802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2050076272027901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.11910970408747</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.4074954172257299</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.41606982531736</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1637562782531401</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D09F-419F-90AF-03E9982671F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lawler (2006)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.9012790067908178E-2"/>
+                  <c:y val="-0.17147116731545345"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$D$4:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.90356607367203301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.84393866538764695</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.90358482744648005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.663434225775831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.66475177086608195</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.238708102284336</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.57708462423306806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$I$4:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.26654667808256899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.541500872594741</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92674759673055396</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.156816283020727</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25880560171696498</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.52921681534296305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.401331670241585</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D09F-419F-90AF-03E9982671F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich (2014) </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.1597300337457817E-3"/>
+                  <c:y val="-0.3785432026348135"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$E$4:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73975142372925395</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14477972148899501</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.8588218215967606E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$J$4:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.57681691180727601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.54443871754473905</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13984116014494999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9326261366187695E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.6283799610675601E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.0850994672477702E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.7271555006068101E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D09F-419F-90AF-03E9982671F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2030081823"/>
+        <c:axId val="1738693935"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2030081823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1738693935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1738693935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2030081823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Spring SSC HI to Turbidity HI  </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.13638095238095238"/>
+          <c:y val="4.8096202503948055E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Langlois (2005)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.43146544181977253"/>
+                  <c:y val="-3.6791338582677122E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$C$11:$C$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.86943505833322</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3545954270153699</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.31746197777344</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.89735303995633098</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.39880081037808</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2210038373368299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5249018262283101</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.36678278361715</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.8695993339197901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.21795864622288</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.0299659938988901</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1534447144942801</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.6625275928143599</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.83858009935182098</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.31938512736013</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.66955637894203</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.90805045415642205</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.0862889042163599</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.39254775269290398</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$H$11:$H$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="1">
+                  <c:v>1.39679058575205</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2576523908335999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.24807759229999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.42877693896201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.33941755807892</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3769164984553499</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.5749763159783401</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.05849048577709</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.4368219825375701</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.1632876834321</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.2283054504143001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.2985932043400299</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.25880991704892</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2914529576795399</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.2886907903199001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.15490049713987</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6223687074200499</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.4572146309152101</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7415-4953-9F5C-AF57A8B15178}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lawler (2006)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.9012790067908178E-2"/>
+                  <c:y val="-0.17147116731545345"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$D$11:$D$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>1.9314296164550899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0089470650494099</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66698565105034602</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19762137224995299</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.54807771119966198</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.10106112243990099</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.50902572287082404</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.463447965306029</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.44896728093636801</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5264059910121399</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.71671353985517805</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.678678630991426</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.81343884511072295</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.07855599689062</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.34776836410395</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.55456789410428697</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.373253605455523</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.63056904760694898</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.623899602892661</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$I$11:$I$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>0.178366367675658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88641107886014003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77855192606860901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.55577143716833499</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.33551375674123601</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.63731372986403501</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.44248745305980902</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.78100360785877099</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.73582121336391904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.96854380596042999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.91285830032378401</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.33582626900186402</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.52794332050181203</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.94081849763111403</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.445945938664987</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.136935986249347</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.47813963463856402</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.74242380847501299</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.80433038241724497</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7415-4953-9F5C-AF57A8B15178}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SSC - Turbidity '!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Aich (2014) </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-9.3723897720332128E-2"/>
+                  <c:y val="9.2273310555144747E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$E$11:$E$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>9.4513218106104094E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2663094228711902E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.8732929175135894E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.9463558010346702E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10415722716452799</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.66251429291673E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0894558490112708E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0373962034653699E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4947102971666898E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.6293174744729593E-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.14608753400636901</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.27691539373017E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.7576112725014403E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0119527368219401E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.5646344187588998E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.47909285306715E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.0282132481243099E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.6679485231980898E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.7980025652416296E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SSC - Turbidity '!$J$11:$J$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>5.1856335362832198E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.103368750113241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.15621819275209001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15071577677020101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.5397551503622099E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.9883057908481996E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8645648239850305E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.101236914763633</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4573685986466099E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.198594884621278</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.8212961854365706E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.39411883766970102</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.0698601563059603E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.9852529707758195E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5815481283492403E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.5391388976058394E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.115227328160236</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.157732693122626</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.121156039239802</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7415-4953-9F5C-AF57A8B15178}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2030081823"/>
+        <c:axId val="1738693935"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2030081823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1738693935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1738693935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2030081823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>23811</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1494854B-2009-B927-5BC6-5A9341DAEA81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A920D4F-927D-42B7-9854-256F1CED8F35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -834,7 +3904,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="10"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -843,7 +3913,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="4"/>
-      <c r="K11" s="10"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1613,7 +4683,7 @@
         <v>20</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="10"/>
+      <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2170,4 +5240,867 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B756ED23-9972-49B1-A962-184A6795F72B}">
+  <dimension ref="A2:M30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14">
+        <v>5.5990042925280497</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0.90356607367203301</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0.78479742735639801</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1.7878260187067601</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.26654667808256899</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0.57681691180727601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="14">
+        <v>3.6150481998819401</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0.84393866538764695</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0.73975142372925395</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5" s="8">
+        <v>2.8770644107042802</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.541500872594741</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0.54443871754473905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="14">
+        <v>2.1746388039620901</v>
+      </c>
+      <c r="D6" s="14">
+        <v>0.90358482744648005</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0.17369777575697301</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1.2050076272027901</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0.92674759673055396</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.13984116014494999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2.2792285281778502</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0.663434225775831</v>
+      </c>
+      <c r="E7" s="14">
+        <v>9.9143945152060597E-2</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1.11910970408747</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0.156816283020727</v>
+      </c>
+      <c r="J7" s="8">
+        <v>8.9326261366187695E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="14">
+        <v>1.4480475262282899</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0.66475177086608195</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0.21234239309632399</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1.4074954172257299</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.25880560171696498</v>
+      </c>
+      <c r="J8" s="8">
+        <v>4.6283799610675601E-2</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14">
+        <v>1.45242884682964</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0.238708102284336</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0.14477972148899501</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1.41606982531736</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.52921681534296305</v>
+      </c>
+      <c r="J9" s="8">
+        <v>3.0850994672477702E-2</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="14">
+        <v>0.84619083652769</v>
+      </c>
+      <c r="D10" s="14">
+        <v>-0.57708462423306806</v>
+      </c>
+      <c r="E10" s="14">
+        <v>-7.8588218215967606E-2</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1.1637562782531401</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.401331670241585</v>
+      </c>
+      <c r="J10" s="8">
+        <v>6.7271555006068101E-2</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="15">
+        <v>1.86943505833322</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1.9314296164550899</v>
+      </c>
+      <c r="E11" s="15">
+        <v>9.4513218106104094E-2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20">
+        <v>0.178366367675658</v>
+      </c>
+      <c r="J11" s="20">
+        <v>5.1856335362832198E-2</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="11"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="15">
+        <v>1.3545954270153699</v>
+      </c>
+      <c r="D12" s="15">
+        <v>1.0089470650494099</v>
+      </c>
+      <c r="E12" s="15">
+        <v>4.2663094228711902E-2</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="20">
+        <v>1.39679058575205</v>
+      </c>
+      <c r="I12" s="20">
+        <v>0.88641107886014003</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.103368750113241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="15">
+        <v>1.31746197777344</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0.66698565105034602</v>
+      </c>
+      <c r="E13" s="15">
+        <v>8.8732929175135894E-2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="20">
+        <v>1.2576523908335999</v>
+      </c>
+      <c r="I13" s="20">
+        <v>0.77855192606860901</v>
+      </c>
+      <c r="J13" s="20">
+        <v>0.15621819275209001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0.89735303995633098</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0.19762137224995299</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-1.9463558010346702E-2</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="20">
+        <v>1.24807759229999</v>
+      </c>
+      <c r="I14" s="20">
+        <v>0.55577143716833499</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0.15071577677020101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="15">
+        <v>1.39880081037808</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0.54807771119966198</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0.10415722716452799</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="20">
+        <v>1.42877693896201</v>
+      </c>
+      <c r="I15" s="20">
+        <v>0.33551375674123601</v>
+      </c>
+      <c r="J15" s="20">
+        <v>5.5397551503622099E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="15">
+        <v>1.2210038373368299</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0.10106112243990099</v>
+      </c>
+      <c r="E16" s="15">
+        <v>4.66251429291673E-2</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="20">
+        <v>1.33941755807892</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0.63731372986403501</v>
+      </c>
+      <c r="J16" s="20">
+        <v>6.9883057908481996E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1.5249018262283101</v>
+      </c>
+      <c r="D17" s="15">
+        <v>0.50902572287082404</v>
+      </c>
+      <c r="E17" s="15">
+        <v>9.0894558490112708E-3</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="20">
+        <v>1.3769164984553499</v>
+      </c>
+      <c r="I17" s="20">
+        <v>-0.44248745305980902</v>
+      </c>
+      <c r="J17" s="20">
+        <v>7.8645648239850305E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="15">
+        <v>1.36678278361715</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0.463447965306029</v>
+      </c>
+      <c r="E18" s="15">
+        <v>2.0373962034653699E-2</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="20">
+        <v>1.5749763159783401</v>
+      </c>
+      <c r="I18" s="20">
+        <v>0.78100360785877099</v>
+      </c>
+      <c r="J18" s="20">
+        <v>0.101236914763633</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1.8695993339197901</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0.44896728093636801</v>
+      </c>
+      <c r="E19" s="15">
+        <v>2.4947102971666898E-2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="20">
+        <v>1.05849048577709</v>
+      </c>
+      <c r="I19" s="20">
+        <v>-0.73582121336391904</v>
+      </c>
+      <c r="J19" s="20">
+        <v>8.4573685986466099E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1.21795864622288</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1.5264059910121399</v>
+      </c>
+      <c r="E20" s="15">
+        <v>9.6293174744729593E-3</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="20">
+        <v>1.4368219825375701</v>
+      </c>
+      <c r="I20" s="20">
+        <v>0.96854380596042999</v>
+      </c>
+      <c r="J20" s="20">
+        <v>0.198594884621278</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1.0299659938988901</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0.71671353985517805</v>
+      </c>
+      <c r="E21" s="15">
+        <v>0.14608753400636901</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="20">
+        <v>1.1632876834321</v>
+      </c>
+      <c r="I21" s="20">
+        <v>0.91285830032378401</v>
+      </c>
+      <c r="J21" s="20">
+        <v>6.8212961854365706E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="15">
+        <v>1.1534447144942801</v>
+      </c>
+      <c r="D22" s="15">
+        <v>0.678678630991426</v>
+      </c>
+      <c r="E22" s="15">
+        <v>1.27691539373017E-2</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="20">
+        <v>1.2283054504143001</v>
+      </c>
+      <c r="I22" s="20">
+        <v>0.33582626900186402</v>
+      </c>
+      <c r="J22" s="20">
+        <v>0.39411883766970102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="15">
+        <v>1.6625275928143599</v>
+      </c>
+      <c r="D23" s="15">
+        <v>0.81343884511072295</v>
+      </c>
+      <c r="E23" s="15">
+        <v>6.7576112725014403E-2</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="20">
+        <v>1.2985932043400299</v>
+      </c>
+      <c r="I23" s="20">
+        <v>0.52794332050181203</v>
+      </c>
+      <c r="J23" s="20">
+        <v>9.0698601563059603E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="15">
+        <v>0.83858009935182098</v>
+      </c>
+      <c r="D24" s="15">
+        <v>-1.07855599689062</v>
+      </c>
+      <c r="E24" s="15">
+        <v>1.0119527368219401E-2</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="20">
+        <v>1.25880991704892</v>
+      </c>
+      <c r="I24" s="20">
+        <v>0.94081849763111403</v>
+      </c>
+      <c r="J24" s="20">
+        <v>9.9852529707758195E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="15">
+        <v>2.31938512736013</v>
+      </c>
+      <c r="D25" s="15">
+        <v>1.34776836410395</v>
+      </c>
+      <c r="E25" s="15">
+        <v>4.5646344187588998E-2</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="20">
+        <v>1.2914529576795399</v>
+      </c>
+      <c r="I25" s="20">
+        <v>0.445945938664987</v>
+      </c>
+      <c r="J25" s="20">
+        <v>5.5815481283492403E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1.66955637894203</v>
+      </c>
+      <c r="D26" s="15">
+        <v>0.55456789410428697</v>
+      </c>
+      <c r="E26" s="15">
+        <v>1.47909285306715E-2</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H26" s="20">
+        <v>1.2886907903199001</v>
+      </c>
+      <c r="I26" s="20">
+        <v>-0.136935986249347</v>
+      </c>
+      <c r="J26" s="20">
+        <v>9.5391388976058394E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="15">
+        <v>0.90805045415642205</v>
+      </c>
+      <c r="D27" s="15">
+        <v>-0.373253605455523</v>
+      </c>
+      <c r="E27" s="15">
+        <v>2.0282132481243099E-2</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="20">
+        <v>1.15490049713987</v>
+      </c>
+      <c r="I27" s="20">
+        <v>0.47813963463856402</v>
+      </c>
+      <c r="J27" s="20">
+        <v>0.115227328160236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="15">
+        <v>1.0862889042163599</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0.63056904760694898</v>
+      </c>
+      <c r="E28" s="15">
+        <v>3.6679485231980898E-2</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H28" s="20">
+        <v>1.6223687074200499</v>
+      </c>
+      <c r="I28" s="20">
+        <v>0.74242380847501299</v>
+      </c>
+      <c r="J28" s="20">
+        <v>0.157732693122626</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="15">
+        <v>0.39254775269290398</v>
+      </c>
+      <c r="D29" s="15">
+        <v>-0.623899602892661</v>
+      </c>
+      <c r="E29" s="15">
+        <v>7.7980025652416296E-2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="20">
+        <v>1.4572146309152101</v>
+      </c>
+      <c r="I29" s="20">
+        <v>0.80433038241724497</v>
+      </c>
+      <c r="J29" s="20">
+        <v>0.121156039239802</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/hysteresis_summary.xlsx
+++ b/hysteresis_summary.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A391F6-4573-4525-8A1F-57AE0952071D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE9DD82-26B6-4723-AC3E-E1EEED0DD595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="SSC - Turbidity " sheetId="2" r:id="rId2"/>
+    <sheet name="HI analysis paper" sheetId="3" r:id="rId1"/>
+    <sheet name="All " sheetId="1" r:id="rId2"/>
+    <sheet name="SSC - Turbidity " sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="73">
   <si>
     <t>Storm</t>
   </si>
@@ -170,16 +171,107 @@
   <si>
     <t>U</t>
   </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>Drise</t>
+  </si>
+  <si>
+    <t>Dfall</t>
+  </si>
+  <si>
+    <t>storm</t>
+  </si>
+  <si>
+    <t>st1</t>
+  </si>
+  <si>
+    <t>st2</t>
+  </si>
+  <si>
+    <t>st3</t>
+  </si>
+  <si>
+    <t>st4</t>
+  </si>
+  <si>
+    <t>st5</t>
+  </si>
+  <si>
+    <t>st6</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>POC</t>
+  </si>
+  <si>
+    <t>DOC</t>
+  </si>
+  <si>
+    <t>SRP</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aich HI </t>
+  </si>
+  <si>
+    <t>Turbidity</t>
+  </si>
+  <si>
+    <t>fDOM</t>
+  </si>
+  <si>
+    <t>Summer Storms</t>
+  </si>
+  <si>
+    <t>event 1</t>
+  </si>
+  <si>
+    <t>event2</t>
+  </si>
+  <si>
+    <t>event3</t>
+  </si>
+  <si>
+    <t>event4</t>
+  </si>
+  <si>
+    <t>event5</t>
+  </si>
+  <si>
+    <t>event6</t>
+  </si>
+  <si>
+    <t>event7</t>
+  </si>
+  <si>
+    <t>event8</t>
+  </si>
+  <si>
+    <t>event9</t>
+  </si>
+  <si>
+    <t>event10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -235,7 +327,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -243,11 +335,274 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -276,11 +631,7 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -289,7 +640,7 @@
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -302,7 +653,147 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -323,6 +814,1936 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Summer SS</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> HI to Others HI</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23566897203542989"/>
+          <c:y val="9.2592592592592587E-3"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$Q$2:$S$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>POC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.46282261592300961"/>
+                  <c:y val="-4.5585812190142898E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="25000"/>
+                    <a:lumOff val="75000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$Q$4:$Q$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.735611704001494</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.199680501000808</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.12535086320927399</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42964915677977999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.3375577562074601E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5262412029273197E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$F$2:$H$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DOC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.36073720711918311"/>
+                  <c:y val="-0.50087051618547684"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$F$4:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>-0.69015600278604705</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7836570943256701E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.54160608613664096</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.17637365181995501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39449354239977702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.17371472956907899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$T$2:$V$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.26341360614594711"/>
+                  <c:y val="-0.11869386118401866"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$T$4:$T$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.45797375947830898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.14905336293267299</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.08380665362574E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$W$2:$Y$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SRP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.13364880484829908"/>
+                  <c:y val="-0.31863918051910178"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$W$4:$W$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>-4.4193639828931201E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.6875193364792196E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.6669485065099E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.59517217205262E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.155085326236896</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.49269779802698299</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$Z$2:$AB$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.9836963810180663E-2"/>
+                  <c:y val="-0.15069152814231554"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$Z$4:$Z$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.37069968925848601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10077650528672399</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.3493902184217604E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'HI analysis paper'!$I$2:$K$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Turbidity</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.9806182986250802E-2"/>
+                  <c:y val="-0.17287292213473315"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$I$4:$I$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.57681691180727601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13233171245622599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9326261366187695E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6283799610675601E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.164262280281398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.45444212598241E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7D61-4C90-93D8-FD403BC9B80C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="442023904"/>
+        <c:axId val="663387696"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="442023904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="663387696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="663387696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="442023904"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="8"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="9"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="10"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="11"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Constituent</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs Sonde HI</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>SSC-Turbidity</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.38341863517060365"/>
+                  <c:y val="3.3238553514144489E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$C$4:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.4513218106104094E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.2663094228711902E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.8732929175135894E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.9463558010346702E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.10415722716452799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.66251429291673E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.0894558490112708E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1.7278096303121701E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0373962034653699E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-2.50118292734785E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$I$4:$I$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>0.57681691180727601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13233171245622599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9326261366187695E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6283799610675601E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.164262280281398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.45444212598241E-2</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>5.1856335362832198E-2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>0.103368750113241</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>0.15621819275209001</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>0.15071577677020101</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.000">
+                  <c:v>5.5397551503622099E-2</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>6.9883057908481996E-2</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>7.8645648239850305E-2</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>2.1496979213356301E-3</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.000">
+                  <c:v>0.101236914763633</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0.000">
+                  <c:v>0.107400232693555</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E07A-4711-81C7-DABCF8E72C8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>DOC-fDOM</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.1900043744531933E-2"/>
+                  <c:y val="0.29082057451151938"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$F$4:$F$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>-0.69015600278604705</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7836570943256701E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.54160608613664096</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.17637365181995501</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39449354239977702</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.17371472956907899</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4332675043980999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.8668980226143202E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.20306787922476E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.7386597361713599E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.8615745110634201E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.4113621235337297E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-8.0536265843332393E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.13677287576714E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.7450804091866201E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.0077224600602597E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'HI analysis paper'!$L$4:$L$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>-0.62489073949006502</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.64117535564386996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.511670862423525</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.22155858359451899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.6450074853088597E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.24313716774511701</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.000">
+                  <c:v>1.3430417175947699E-2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.000">
+                  <c:v>-1.61778645652975E-2</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.000">
+                  <c:v>2.95836818188689E-2</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.000">
+                  <c:v>-5.4892758010415703E-2</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.000">
+                  <c:v>8.8641812543785899E-3</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.000">
+                  <c:v>1.32778322661357E-2</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.000">
+                  <c:v>-6.0975544853349099E-2</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.000">
+                  <c:v>-1.77749404385871E-2</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.000">
+                  <c:v>3.08855730575289E-3</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0.000">
+                  <c:v>-5.3081166180475401E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E07A-4711-81C7-DABCF8E72C8C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="904648112"/>
+        <c:axId val="663504336"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="904648112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="663504336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="663504336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904648112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3121097987751531"/>
+          <c:y val="0.89698964712744245"/>
+          <c:w val="0.41309009176373535"/>
+          <c:h val="7.8125546806649182E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1109,7 +3530,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2189,6 +4610,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3221,7 +5722,1116 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>213633</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38779</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>477611</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>132669</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{536C5A4E-6BA1-1B19-D8C6-C4B41177BC62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>490537</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17F5BA9A-42EF-B7C5-6C0D-CA048EFBB323}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3616,6 +7226,1124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921FD224-7274-4735-BBE2-BB79D8865705}">
+  <dimension ref="A1:AB33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.42578125" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" customWidth="1"/>
+    <col min="20" max="20" width="17" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B2" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="27"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" s="27"/>
+      <c r="N2" s="28"/>
+      <c r="Q2" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="27"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="27"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="28"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B3" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z3" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB3" s="30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="43">
+        <v>0.78479742735639801</v>
+      </c>
+      <c r="D4" s="22">
+        <v>0.70362334277140404</v>
+      </c>
+      <c r="E4" s="31">
+        <v>8.1174084584993894E-2</v>
+      </c>
+      <c r="F4" s="46">
+        <v>-0.69015600278604705</v>
+      </c>
+      <c r="G4" s="22">
+        <v>-0.62535269101711499</v>
+      </c>
+      <c r="H4" s="34">
+        <v>-6.4803311768931199E-2</v>
+      </c>
+      <c r="I4" s="43">
+        <v>0.57681691180727601</v>
+      </c>
+      <c r="J4" s="22">
+        <v>0.46622115335576803</v>
+      </c>
+      <c r="K4" s="34">
+        <v>0.110595758451508</v>
+      </c>
+      <c r="L4" s="46">
+        <v>-0.62489073949006502</v>
+      </c>
+      <c r="M4" s="22">
+        <v>-0.150232081100411</v>
+      </c>
+      <c r="N4" s="31">
+        <v>-0.47465865838965399</v>
+      </c>
+      <c r="P4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="43">
+        <v>0.735611704001494</v>
+      </c>
+      <c r="R4" s="22">
+        <v>0.69646761676225899</v>
+      </c>
+      <c r="S4" s="31">
+        <v>3.9144087239235598E-2</v>
+      </c>
+      <c r="T4" s="50">
+        <v>0.45797375947830898</v>
+      </c>
+      <c r="U4" s="22">
+        <v>0.37039120056534902</v>
+      </c>
+      <c r="V4" s="31">
+        <v>8.7582558912959393E-2</v>
+      </c>
+      <c r="W4" s="48">
+        <v>-4.4193639828931201E-2</v>
+      </c>
+      <c r="X4" s="22">
+        <v>-6.3205098425588996E-2</v>
+      </c>
+      <c r="Y4" s="31">
+        <v>1.9011458596657801E-2</v>
+      </c>
+      <c r="Z4" s="50">
+        <v>0.37069968925848601</v>
+      </c>
+      <c r="AA4" s="22">
+        <v>0.33347773016015803</v>
+      </c>
+      <c r="AB4" s="31">
+        <v>3.7221959098327602E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="43">
+        <v>0.17369777575697301</v>
+      </c>
+      <c r="D5" s="22">
+        <v>0.15689425896952999</v>
+      </c>
+      <c r="E5" s="31">
+        <v>1.6803516787443101E-2</v>
+      </c>
+      <c r="F5" s="43">
+        <v>1.7836570943256701E-2</v>
+      </c>
+      <c r="G5" s="22">
+        <v>7.3849978099684202E-2</v>
+      </c>
+      <c r="H5" s="34">
+        <v>-5.60134071564274E-2</v>
+      </c>
+      <c r="I5" s="43">
+        <v>0.13233171245622599</v>
+      </c>
+      <c r="J5" s="22">
+        <v>0.21566765129718499</v>
+      </c>
+      <c r="K5" s="34">
+        <v>-8.3335938840959495E-2</v>
+      </c>
+      <c r="L5" s="46">
+        <v>-0.64117535564386996</v>
+      </c>
+      <c r="M5" s="22">
+        <v>-0.57016699616469202</v>
+      </c>
+      <c r="N5" s="31">
+        <v>-7.1008359479177996E-2</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="43">
+        <v>0.199680501000808</v>
+      </c>
+      <c r="R5" s="22">
+        <v>0.16274944235821701</v>
+      </c>
+      <c r="S5" s="31">
+        <v>3.6931058642590602E-2</v>
+      </c>
+      <c r="T5" s="50">
+        <v>0.14905336293267299</v>
+      </c>
+      <c r="U5" s="22">
+        <v>0.13280569924708099</v>
+      </c>
+      <c r="V5" s="31">
+        <v>1.6247663685591999E-2</v>
+      </c>
+      <c r="W5" s="50">
+        <v>6.6875193364792196E-2</v>
+      </c>
+      <c r="X5" s="22">
+        <v>7.4483108383515004E-2</v>
+      </c>
+      <c r="Y5" s="31">
+        <v>-7.6079150187227298E-3</v>
+      </c>
+      <c r="Z5" s="50">
+        <v>0.10077650528672399</v>
+      </c>
+      <c r="AA5" s="22">
+        <v>0.115517525518831</v>
+      </c>
+      <c r="AB5" s="31">
+        <v>-1.47410202321074E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="43">
+        <v>9.9143945152060597E-2</v>
+      </c>
+      <c r="D6" s="22">
+        <v>6.6581899186216403E-2</v>
+      </c>
+      <c r="E6" s="31">
+        <v>3.2562045965844201E-2</v>
+      </c>
+      <c r="F6" s="46">
+        <v>-0.54160608613664096</v>
+      </c>
+      <c r="G6" s="22">
+        <v>-0.48071854313835499</v>
+      </c>
+      <c r="H6" s="34">
+        <v>-6.0887542998285603E-2</v>
+      </c>
+      <c r="I6" s="43">
+        <v>8.9326261366187695E-2</v>
+      </c>
+      <c r="J6" s="22">
+        <v>3.99515326400596E-2</v>
+      </c>
+      <c r="K6" s="34">
+        <v>4.9374728726128102E-2</v>
+      </c>
+      <c r="L6" s="46">
+        <v>-0.511670862423525</v>
+      </c>
+      <c r="M6" s="22">
+        <v>-0.429115164593801</v>
+      </c>
+      <c r="N6" s="31">
+        <v>-8.2555697829723301E-2</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q6" s="43">
+        <v>0.12535086320927399</v>
+      </c>
+      <c r="R6" s="22">
+        <v>5.74900289420502E-2</v>
+      </c>
+      <c r="S6" s="31">
+        <v>6.7860834267224501E-2</v>
+      </c>
+      <c r="T6" s="48">
+        <v>-1.08380665362574E-2</v>
+      </c>
+      <c r="U6" s="22">
+        <v>-4.0397841472139699E-2</v>
+      </c>
+      <c r="V6" s="31">
+        <v>2.9559774935882299E-2</v>
+      </c>
+      <c r="W6" s="48">
+        <v>-8.6669485065099E-2</v>
+      </c>
+      <c r="X6" s="22">
+        <v>-9.6275824598921797E-2</v>
+      </c>
+      <c r="Y6" s="31">
+        <v>9.6063395338228802E-3</v>
+      </c>
+      <c r="Z6" s="50">
+        <v>6.3493902184217604E-2</v>
+      </c>
+      <c r="AA6" s="22">
+        <v>2.97169838450441E-2</v>
+      </c>
+      <c r="AB6" s="31">
+        <v>3.3776918339173401E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="43">
+        <v>0.21234239309632399</v>
+      </c>
+      <c r="D7" s="22">
+        <v>0.296918924826297</v>
+      </c>
+      <c r="E7" s="31">
+        <v>-8.4576531729973606E-2</v>
+      </c>
+      <c r="F7" s="46">
+        <v>-0.17637365181995501</v>
+      </c>
+      <c r="G7" s="22">
+        <v>-0.201204396110124</v>
+      </c>
+      <c r="H7" s="34">
+        <v>2.4830744290168998E-2</v>
+      </c>
+      <c r="I7" s="43">
+        <v>4.6283799610675601E-2</v>
+      </c>
+      <c r="J7" s="22">
+        <v>9.8947685932445406E-2</v>
+      </c>
+      <c r="K7" s="34">
+        <v>-5.2663886321769798E-2</v>
+      </c>
+      <c r="L7" s="46">
+        <v>-0.22155858359451899</v>
+      </c>
+      <c r="M7" s="22">
+        <v>7.9190642894289398E-2</v>
+      </c>
+      <c r="N7" s="31">
+        <v>-0.30074922648880797</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="43">
+        <v>0.42964915677977999</v>
+      </c>
+      <c r="R7" s="22">
+        <v>0.39478228720937197</v>
+      </c>
+      <c r="S7" s="31">
+        <v>3.4866869570408E-2</v>
+      </c>
+      <c r="T7" s="57"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="50">
+        <v>3.59517217205262E-2</v>
+      </c>
+      <c r="X7" s="22">
+        <v>4.8333794755950399E-2</v>
+      </c>
+      <c r="Y7" s="31">
+        <v>-1.23820730354241E-2</v>
+      </c>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="31"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="43">
+        <v>0.36516163611226798</v>
+      </c>
+      <c r="D8" s="22">
+        <v>0.28872709507702199</v>
+      </c>
+      <c r="E8" s="31">
+        <v>7.6434541035245399E-2</v>
+      </c>
+      <c r="F8" s="43">
+        <v>0.39449354239977702</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.37634771546754597</v>
+      </c>
+      <c r="H8" s="34">
+        <v>1.8145826932230699E-2</v>
+      </c>
+      <c r="I8" s="43">
+        <v>0.164262280281398</v>
+      </c>
+      <c r="J8" s="22">
+        <v>0.198038148241589</v>
+      </c>
+      <c r="K8" s="34">
+        <v>-3.37758679601909E-2</v>
+      </c>
+      <c r="L8" s="43">
+        <v>9.6450074853088597E-2</v>
+      </c>
+      <c r="M8" s="22">
+        <v>0.128353231708594</v>
+      </c>
+      <c r="N8" s="31">
+        <v>-3.1903156855505599E-2</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" s="43">
+        <v>4.3375577562074601E-2</v>
+      </c>
+      <c r="R8" s="22">
+        <v>4.3375577562074399E-2</v>
+      </c>
+      <c r="S8" s="31">
+        <v>1.6332722649176301E-16</v>
+      </c>
+      <c r="T8" s="57"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="50">
+        <v>0.155085326236896</v>
+      </c>
+      <c r="X8" s="22">
+        <v>0.41456430567006802</v>
+      </c>
+      <c r="Y8" s="31">
+        <v>-0.259478979433171</v>
+      </c>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="31"/>
+    </row>
+    <row r="9" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="52">
+        <v>4.1333778886518201E-2</v>
+      </c>
+      <c r="D9" s="53">
+        <v>4.1365977031752599E-3</v>
+      </c>
+      <c r="E9" s="54">
+        <v>3.7197181183342899E-2</v>
+      </c>
+      <c r="F9" s="55">
+        <v>-0.17371472956907899</v>
+      </c>
+      <c r="G9" s="53">
+        <v>-0.19619634597505001</v>
+      </c>
+      <c r="H9" s="56">
+        <v>2.24816164059711E-2</v>
+      </c>
+      <c r="I9" s="55">
+        <v>-4.45444212598241E-2</v>
+      </c>
+      <c r="J9" s="53">
+        <v>5.30727244505E-2</v>
+      </c>
+      <c r="K9" s="56">
+        <v>-9.7617145710324205E-2</v>
+      </c>
+      <c r="L9" s="55">
+        <v>-0.24313716774511701</v>
+      </c>
+      <c r="M9" s="53">
+        <v>-0.15475673171724699</v>
+      </c>
+      <c r="N9" s="54">
+        <v>-8.8380436027870005E-2</v>
+      </c>
+      <c r="P9" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="44">
+        <v>4.5262412029273197E-2</v>
+      </c>
+      <c r="R9" s="32">
+        <v>5.4155752333750098E-2</v>
+      </c>
+      <c r="S9" s="33">
+        <v>-8.8933403044769502E-3</v>
+      </c>
+      <c r="T9" s="58"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="49">
+        <v>-0.49269779802698299</v>
+      </c>
+      <c r="X9" s="32">
+        <v>-0.22452001643226499</v>
+      </c>
+      <c r="Y9" s="33">
+        <v>-0.268177781594718</v>
+      </c>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="33"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="43">
+        <v>9.4513218106104094E-2</v>
+      </c>
+      <c r="D10" s="22">
+        <v>8.7712025060473403E-2</v>
+      </c>
+      <c r="E10" s="31">
+        <v>6.8011930456306499E-3</v>
+      </c>
+      <c r="F10" s="43">
+        <v>3.4332675043980999E-2</v>
+      </c>
+      <c r="G10" s="22">
+        <v>5.8887610419738098E-2</v>
+      </c>
+      <c r="H10" s="34">
+        <v>-2.4554935375756998E-2</v>
+      </c>
+      <c r="I10" s="67">
+        <v>5.1856335362832198E-2</v>
+      </c>
+      <c r="J10" s="59">
+        <v>2.0423537450667899E-16</v>
+      </c>
+      <c r="K10" s="65">
+        <v>5.1856335362831997E-2</v>
+      </c>
+      <c r="L10" s="67">
+        <v>1.3430417175947699E-2</v>
+      </c>
+      <c r="M10" s="59">
+        <v>2.1489651185547499E-16</v>
+      </c>
+      <c r="N10" s="60">
+        <v>1.34304171759475E-2</v>
+      </c>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="43">
+        <v>4.2663094228711902E-2</v>
+      </c>
+      <c r="D11" s="22">
+        <v>3.7485481862699399E-2</v>
+      </c>
+      <c r="E11" s="31">
+        <v>5.1776123660124398E-3</v>
+      </c>
+      <c r="F11" s="43">
+        <v>2.8668980226143202E-2</v>
+      </c>
+      <c r="G11" s="22">
+        <v>3.7753099339109197E-2</v>
+      </c>
+      <c r="H11" s="34">
+        <v>-9.0841191129659698E-3</v>
+      </c>
+      <c r="I11" s="67">
+        <v>0.103368750113241</v>
+      </c>
+      <c r="J11" s="59">
+        <v>6.9658615157810203E-2</v>
+      </c>
+      <c r="K11" s="65">
+        <v>3.3710134955431098E-2</v>
+      </c>
+      <c r="L11" s="69">
+        <v>-1.61778645652975E-2</v>
+      </c>
+      <c r="M11" s="59">
+        <v>-3.8003477513916299E-2</v>
+      </c>
+      <c r="N11" s="60">
+        <v>2.1825612948618799E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="43">
+        <v>8.8732929175135894E-2</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0.103305632900852</v>
+      </c>
+      <c r="E12" s="31">
+        <v>-1.4572703725716901E-2</v>
+      </c>
+      <c r="F12" s="43">
+        <v>1.20306787922476E-2</v>
+      </c>
+      <c r="G12" s="22">
+        <v>1.1397484018407599E-2</v>
+      </c>
+      <c r="H12" s="34">
+        <v>6.3319477383991295E-4</v>
+      </c>
+      <c r="I12" s="67">
+        <v>0.15621819275209001</v>
+      </c>
+      <c r="J12" s="59">
+        <v>9.0213507091575995E-2</v>
+      </c>
+      <c r="K12" s="65">
+        <v>6.6004685660513998E-2</v>
+      </c>
+      <c r="L12" s="67">
+        <v>2.95836818188689E-2</v>
+      </c>
+      <c r="M12" s="59">
+        <v>1.7189262626372999E-2</v>
+      </c>
+      <c r="N12" s="60">
+        <v>1.2394419192495801E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="46">
+        <v>-1.9463558010346702E-2</v>
+      </c>
+      <c r="D13" s="22">
+        <v>7.55871132982361E-2</v>
+      </c>
+      <c r="E13" s="31">
+        <v>-9.5050671308582801E-2</v>
+      </c>
+      <c r="F13" s="43">
+        <v>2.7386597361713599E-2</v>
+      </c>
+      <c r="G13" s="22">
+        <v>4.9178342388593199E-2</v>
+      </c>
+      <c r="H13" s="34">
+        <v>-2.17917450268795E-2</v>
+      </c>
+      <c r="I13" s="67">
+        <v>0.15071577677020101</v>
+      </c>
+      <c r="J13" s="59">
+        <v>7.6140386526944506E-2</v>
+      </c>
+      <c r="K13" s="65">
+        <v>7.4575390243256504E-2</v>
+      </c>
+      <c r="L13" s="69">
+        <v>-5.4892758010415703E-2</v>
+      </c>
+      <c r="M13" s="59">
+        <v>-3.1613025723716201E-2</v>
+      </c>
+      <c r="N13" s="60">
+        <v>-2.3279732286699498E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="43">
+        <v>0.10415722716452799</v>
+      </c>
+      <c r="D14" s="22">
+        <v>3.9550625241660302E-2</v>
+      </c>
+      <c r="E14" s="31">
+        <v>6.4606601922867601E-2</v>
+      </c>
+      <c r="F14" s="43">
+        <v>2.8615745110634201E-2</v>
+      </c>
+      <c r="G14" s="22">
+        <v>1.5655706339127499E-2</v>
+      </c>
+      <c r="H14" s="34">
+        <v>1.29600387715066E-2</v>
+      </c>
+      <c r="I14" s="67">
+        <v>5.5397551503622099E-2</v>
+      </c>
+      <c r="J14" s="59">
+        <v>3.4974445332344298E-2</v>
+      </c>
+      <c r="K14" s="65">
+        <v>2.04231061712777E-2</v>
+      </c>
+      <c r="L14" s="67">
+        <v>8.8641812543785899E-3</v>
+      </c>
+      <c r="M14" s="59">
+        <v>2.1843256898497299E-2</v>
+      </c>
+      <c r="N14" s="60">
+        <v>-1.2979075644118701E-2</v>
+      </c>
+      <c r="O14" s="63"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="43">
+        <v>4.66251429291673E-2</v>
+      </c>
+      <c r="D15" s="22">
+        <v>2.7724941830519399E-2</v>
+      </c>
+      <c r="E15" s="31">
+        <v>1.8900201098647901E-2</v>
+      </c>
+      <c r="F15" s="43">
+        <v>4.4113621235337297E-2</v>
+      </c>
+      <c r="G15" s="22">
+        <v>3.4295159201567497E-2</v>
+      </c>
+      <c r="H15" s="34">
+        <v>9.8184620337697492E-3</v>
+      </c>
+      <c r="I15" s="67">
+        <v>6.9883057908481996E-2</v>
+      </c>
+      <c r="J15" s="59">
+        <v>2.1045770316228E-2</v>
+      </c>
+      <c r="K15" s="65">
+        <v>4.8837287592253899E-2</v>
+      </c>
+      <c r="L15" s="67">
+        <v>1.32778322661357E-2</v>
+      </c>
+      <c r="M15" s="59">
+        <v>2.92159140129164E-2</v>
+      </c>
+      <c r="N15" s="60">
+        <v>-1.59380817467807E-2</v>
+      </c>
+      <c r="O15" s="63"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="43">
+        <v>9.0894558490112708E-3</v>
+      </c>
+      <c r="D16" s="22">
+        <v>-3.3760512516220801E-3</v>
+      </c>
+      <c r="E16" s="31">
+        <v>1.2465507100633299E-2</v>
+      </c>
+      <c r="F16" s="46">
+        <v>-8.0536265843332393E-3</v>
+      </c>
+      <c r="G16" s="22">
+        <v>-1.2558539350255599E-2</v>
+      </c>
+      <c r="H16" s="34">
+        <v>4.5049127659223904E-3</v>
+      </c>
+      <c r="I16" s="67">
+        <v>7.8645648239850305E-2</v>
+      </c>
+      <c r="J16" s="59">
+        <v>4.7078314101478502E-2</v>
+      </c>
+      <c r="K16" s="65">
+        <v>3.1567334138371698E-2</v>
+      </c>
+      <c r="L16" s="69">
+        <v>-6.0975544853349099E-2</v>
+      </c>
+      <c r="M16" s="59">
+        <v>-4.2184853948021302E-2</v>
+      </c>
+      <c r="N16" s="60">
+        <v>-1.8790690905327801E-2</v>
+      </c>
+      <c r="O16" s="63"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="46">
+        <v>-1.7278096303121701E-2</v>
+      </c>
+      <c r="D17" s="22">
+        <v>-1.6265992924389699E-16</v>
+      </c>
+      <c r="E17" s="31">
+        <v>-1.72780963031216E-2</v>
+      </c>
+      <c r="F17" s="46">
+        <v>-2.13677287576714E-2</v>
+      </c>
+      <c r="G17" s="22">
+        <v>2.16339597252613E-16</v>
+      </c>
+      <c r="H17" s="34">
+        <v>-2.1367728757671602E-2</v>
+      </c>
+      <c r="I17" s="67">
+        <v>2.1496979213356301E-3</v>
+      </c>
+      <c r="J17" s="59">
+        <v>6.03514533009855E-2</v>
+      </c>
+      <c r="K17" s="65">
+        <v>-5.8201755379649903E-2</v>
+      </c>
+      <c r="L17" s="69">
+        <v>-1.77749404385871E-2</v>
+      </c>
+      <c r="M17" s="59">
+        <v>2.3297171947637099E-2</v>
+      </c>
+      <c r="N17" s="60">
+        <v>-4.1072112386224303E-2</v>
+      </c>
+      <c r="O17" s="63"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="43">
+        <v>2.0373962034653699E-2</v>
+      </c>
+      <c r="D18" s="22">
+        <v>1.2046196031845801E-2</v>
+      </c>
+      <c r="E18" s="31">
+        <v>8.3277660028078706E-3</v>
+      </c>
+      <c r="F18" s="43">
+        <v>2.7450804091866201E-2</v>
+      </c>
+      <c r="G18" s="22">
+        <v>1.45293942449428E-2</v>
+      </c>
+      <c r="H18" s="34">
+        <v>1.2921409846923399E-2</v>
+      </c>
+      <c r="I18" s="67">
+        <v>0.101236914763633</v>
+      </c>
+      <c r="J18" s="59">
+        <v>7.1143773259400994E-2</v>
+      </c>
+      <c r="K18" s="65">
+        <v>3.0093141504232802E-2</v>
+      </c>
+      <c r="L18" s="67">
+        <v>3.08855730575289E-3</v>
+      </c>
+      <c r="M18" s="59">
+        <v>3.05061931580645E-2</v>
+      </c>
+      <c r="N18" s="60">
+        <v>-2.7417635852311599E-2</v>
+      </c>
+      <c r="O18" s="63"/>
+    </row>
+    <row r="19" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="47">
+        <v>-2.50118292734785E-2</v>
+      </c>
+      <c r="D19" s="32">
+        <v>0</v>
+      </c>
+      <c r="E19" s="33">
+        <v>-2.50118292734785E-2</v>
+      </c>
+      <c r="F19" s="47">
+        <v>-4.0077224600602597E-2</v>
+      </c>
+      <c r="G19" s="32">
+        <v>-7.53555113400115E-16</v>
+      </c>
+      <c r="H19" s="35">
+        <v>-4.0077224600601903E-2</v>
+      </c>
+      <c r="I19" s="68">
+        <v>0.107400232693555</v>
+      </c>
+      <c r="J19" s="61">
+        <v>6.9966396060748406E-2</v>
+      </c>
+      <c r="K19" s="66">
+        <v>3.7433836632807402E-2</v>
+      </c>
+      <c r="L19" s="70">
+        <v>-5.3081166180475401E-3</v>
+      </c>
+      <c r="M19" s="61">
+        <v>2.2918752207305201E-2</v>
+      </c>
+      <c r="N19" s="62">
+        <v>-2.8226868825352799E-2</v>
+      </c>
+      <c r="O19" s="63"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M20" s="64"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="63"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M21" s="64"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I22" s="20"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="63"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I23" s="20"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I24" s="20"/>
+      <c r="M24" s="64"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I26" s="20"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I27" s="20"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I33" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B27869-60E0-43BF-B7FC-18286E7E1076}">
   <dimension ref="A1:O55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5242,9 +9970,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B756ED23-9972-49B1-A962-184A6795F72B}">
-  <dimension ref="A2:M30"/>
+  <dimension ref="A2:L30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.28515625" customWidth="1"/>
@@ -5259,55 +9987,55 @@
     <col min="12" max="12" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="13" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>5.5990042925280497</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="12">
         <v>0.90356607367203301</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>0.78479742735639801</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="17" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="8">
@@ -5320,20 +10048,20 @@
         <v>0.57681691180727601</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>3.6150481998819401</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="12">
         <v>0.84393866538764695</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>0.73975142372925395</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="8">
@@ -5346,20 +10074,20 @@
         <v>0.54443871754473905</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>2.1746388039620901</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <v>0.90358482744648005</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>0.17369777575697301</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>4</v>
       </c>
       <c r="H6" s="8">
@@ -5372,20 +10100,20 @@
         <v>0.13984116014494999</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="12">
         <v>2.2792285281778502</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>0.663434225775831</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>9.9143945152060597E-2</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="8">
@@ -5398,20 +10126,20 @@
         <v>8.9326261366187695E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="12">
         <v>1.4480475262282899</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>0.66475177086608195</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>0.21234239309632399</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="H8" s="8">
@@ -5423,23 +10151,21 @@
       <c r="J8" s="8">
         <v>4.6283799610675601E-2</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="12">
         <v>1.45242884682964</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="12">
         <v>0.238708102284336</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>0.14477972148899501</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="8">
@@ -5451,23 +10177,21 @@
       <c r="J9" s="8">
         <v>3.0850994672477702E-2</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="12">
         <v>0.84619083652769</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="12">
         <v>-0.57708462423306806</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>-7.8588218215967606E-2</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="17" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="8">
@@ -5479,199 +10203,198 @@
       <c r="J10" s="8">
         <v>6.7271555006068101E-2</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <v>1.86943505833322</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <v>1.9314296164550899</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="13">
         <v>9.4513218106104094E-2</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20">
+      <c r="H11" s="17"/>
+      <c r="I11" s="18">
         <v>0.178366367675658</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="18">
         <v>5.1856335362832198E-2</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>1.3545954270153699</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="13">
         <v>1.0089470650494099</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="13">
         <v>4.2663094228711902E-2</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="18">
         <v>1.39679058575205</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="18">
         <v>0.88641107886014003</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="18">
         <v>0.103368750113241</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>1.31746197777344</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <v>0.66698565105034602</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="13">
         <v>8.8732929175135894E-2</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="18">
         <v>1.2576523908335999</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="18">
         <v>0.77855192606860901</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="18">
         <v>0.15621819275209001</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <v>0.89735303995633098</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <v>0.19762137224995299</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="13">
         <v>-1.9463558010346702E-2</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="18">
         <v>1.24807759229999</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="18">
         <v>0.55577143716833499</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="18">
         <v>0.15071577677020101</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>1.39880081037808</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13">
         <v>0.54807771119966198</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="13">
         <v>0.10415722716452799</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="18">
         <v>1.42877693896201</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="18">
         <v>0.33551375674123601</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="18">
         <v>5.5397551503622099E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>1.2210038373368299</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13">
         <v>0.10106112243990099</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="13">
         <v>4.66251429291673E-2</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="18">
         <v>1.33941755807892</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="18">
         <v>0.63731372986403501</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="18">
         <v>6.9883057908481996E-2</v>
       </c>
     </row>
@@ -5679,31 +10402,31 @@
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13">
         <v>1.5249018262283101</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="13">
         <v>0.50902572287082404</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="13">
         <v>9.0894558490112708E-3</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="18">
         <v>1.3769164984553499</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="18">
         <v>-0.44248745305980902</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="18">
         <v>7.8645648239850305E-2</v>
       </c>
     </row>
@@ -5711,31 +10434,31 @@
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13">
         <v>1.36678278361715</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="13">
         <v>0.463447965306029</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="13">
         <v>2.0373962034653699E-2</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="18">
         <v>1.5749763159783401</v>
       </c>
-      <c r="I18" s="20">
+      <c r="I18" s="18">
         <v>0.78100360785877099</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="18">
         <v>0.101236914763633</v>
       </c>
     </row>
@@ -5743,31 +10466,31 @@
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13">
         <v>1.8695993339197901</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13">
         <v>0.44896728093636801</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="13">
         <v>2.4947102971666898E-2</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="18">
         <v>1.05849048577709</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="18">
         <v>-0.73582121336391904</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="18">
         <v>8.4573685986466099E-2</v>
       </c>
     </row>
@@ -5775,31 +10498,31 @@
       <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <v>1.21795864622288</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <v>1.5264059910121399</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="13">
         <v>9.6293174744729593E-3</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="18">
         <v>1.4368219825375701</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="18">
         <v>0.96854380596042999</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="18">
         <v>0.198594884621278</v>
       </c>
     </row>
@@ -5807,31 +10530,31 @@
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <v>1.0299659938988901</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <v>0.71671353985517805</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="13">
         <v>0.14608753400636901</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="18">
         <v>1.1632876834321</v>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="18">
         <v>0.91285830032378401</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="18">
         <v>6.8212961854365706E-2</v>
       </c>
     </row>
@@ -5839,31 +10562,31 @@
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13">
         <v>1.1534447144942801</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13">
         <v>0.678678630991426</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="13">
         <v>1.27691539373017E-2</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="18">
         <v>1.2283054504143001</v>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="18">
         <v>0.33582626900186402</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="18">
         <v>0.39411883766970102</v>
       </c>
     </row>
@@ -5871,31 +10594,31 @@
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13">
         <v>1.6625275928143599</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13">
         <v>0.81343884511072295</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="13">
         <v>6.7576112725014403E-2</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="18">
         <v>1.2985932043400299</v>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="18">
         <v>0.52794332050181203</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="18">
         <v>9.0698601563059603E-2</v>
       </c>
     </row>
@@ -5903,31 +10626,31 @@
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="13">
         <v>0.83858009935182098</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="13">
         <v>-1.07855599689062</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="13">
         <v>1.0119527368219401E-2</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="18">
         <v>1.25880991704892</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="18">
         <v>0.94081849763111403</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="18">
         <v>9.9852529707758195E-2</v>
       </c>
     </row>
@@ -5935,31 +10658,31 @@
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13">
         <v>2.31938512736013</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="13">
         <v>1.34776836410395</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="13">
         <v>4.5646344187588998E-2</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="18">
         <v>1.2914529576795399</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="18">
         <v>0.445945938664987</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="18">
         <v>5.5815481283492403E-2</v>
       </c>
     </row>
@@ -5967,31 +10690,31 @@
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="13">
         <v>1.66955637894203</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="13">
         <v>0.55456789410428697</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="13">
         <v>1.47909285306715E-2</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="18">
         <v>1.2886907903199001</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="18">
         <v>-0.136935986249347</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="18">
         <v>9.5391388976058394E-2</v>
       </c>
     </row>
@@ -5999,31 +10722,31 @@
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <v>0.90805045415642205</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <v>-0.373253605455523</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="13">
         <v>2.0282132481243099E-2</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="18">
         <v>1.15490049713987</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="18">
         <v>0.47813963463856402</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="18">
         <v>0.115227328160236</v>
       </c>
     </row>
@@ -6031,31 +10754,31 @@
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13">
         <v>1.0862889042163599</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <v>0.63056904760694898</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="13">
         <v>3.6679485231980898E-2</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="18">
         <v>1.6223687074200499</v>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="18">
         <v>0.74242380847501299</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="18">
         <v>0.157732693122626</v>
       </c>
     </row>
@@ -6063,31 +10786,31 @@
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13">
         <v>0.39254775269290398</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13">
         <v>-0.623899602892661</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="13">
         <v>7.7980025652416296E-2</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="18">
         <v>1.4572146309152101</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="18">
         <v>0.80433038241724497</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="18">
         <v>0.121156039239802</v>
       </c>
     </row>
@@ -6095,9 +10818,9 @@
       <c r="A30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
